--- a/Datas/B-战斗配置表.xlsx
+++ b/Datas/B-战斗配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="10"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="battle_rule" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>杨宗水</author>
-    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C2" authorId="0">
@@ -89,35 +88,6 @@
           </rPr>
           <t>中文名
 方便策划维护</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D2" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0:无
-1:Debug 测试战斗
-2:普通战斗
-3:精英战斗
-4:Boss 战斗
-5:事件战斗
-6:教学战斗
-</t>
         </r>
       </text>
     </comment>
@@ -254,6 +224,33 @@
 4:受伤后减少
 5:战斗结束移除
 6:手动移除
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:无
+1:固定值
+2:按层数计算
+3:百分比
+4:标记型
 </t>
         </r>
       </text>
@@ -607,7 +604,7 @@
           </rPr>
           <t xml:space="preserve">
 [[effect_id,value,target]]
-[[effect_id,value,target,param]]
+[[effect_id,value,target,status]]
 0:无
 1:效果来源自己
 2:玩家
@@ -705,7 +702,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="206">
   <si>
     <t>##comment</t>
   </si>
@@ -908,6 +905,9 @@
     <t>跳过行动</t>
   </si>
   <si>
+    <t>恢复灵力</t>
+  </si>
+  <si>
     <t>牌组ID</t>
   </si>
   <si>
@@ -1016,9 +1016,6 @@
     <t>drop_table_id</t>
   </si>
   <si>
-    <t>(list#sep=;),int</t>
-  </si>
-  <si>
     <t>腐化灵鼠</t>
   </si>
   <si>
@@ -1076,9 +1073,6 @@
     <t>猛撞</t>
   </si>
   <si>
-    <t>1,14,2</t>
-  </si>
-  <si>
     <t>藤击</t>
   </si>
   <si>
@@ -1199,6 +1193,9 @@
     <t>结算效果ID</t>
   </si>
   <si>
+    <t>状态效果模式</t>
+  </si>
+  <si>
     <t>每层数值</t>
   </si>
   <si>
@@ -1232,6 +1229,9 @@
     <t>tick_effect_id</t>
   </si>
   <si>
+    <t>effect_mode</t>
+  </si>
+  <si>
     <t>value_per_stack</t>
   </si>
   <si>
@@ -1254,6 +1254,9 @@
   </si>
   <si>
     <t>EStatusRemoveTiming</t>
+  </si>
+  <si>
+    <t>EStatusEffectMode</t>
   </si>
   <si>
     <t>力量</t>
@@ -1329,7 +1332,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1349,6 +1352,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF080808"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1826,137 +1835,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1973,28 +1982,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2336,7 +2336,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2489,7 +2489,7 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -2548,22 +2548,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>10</v>
@@ -2574,20 +2574,20 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>20</v>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="3" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>22</v>
@@ -2611,7 +2611,7 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
@@ -2662,34 +2662,34 @@
       </c>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7" s="6">
+        <v>2</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>144</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="9">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="8">
-        <v>2</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -2697,22 +2697,22 @@
       <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="F7" s="9">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>146</v>
+      <c r="C8" s="8" t="s">
+        <v>145</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -2720,22 +2720,22 @@
       <c r="E8" s="4">
         <v>3</v>
       </c>
-      <c r="F8" s="9">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="F8" s="8">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>147</v>
+      <c r="C9" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -2743,22 +2743,22 @@
       <c r="E9" s="4">
         <v>1</v>
       </c>
-      <c r="F9" s="9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" s="6">
-        <v>4</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>147</v>
+        <v>5</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="D10" s="4">
         <v>2</v>
@@ -2766,22 +2766,22 @@
       <c r="E10" s="4">
         <v>2</v>
       </c>
-      <c r="F10" s="9">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:8">
       <c r="B11" s="6">
-        <v>4</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>147</v>
+        <v>6</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="D11" s="4">
         <v>3</v>
@@ -2789,13 +2789,13 @@
       <c r="E11" s="4">
         <v>3</v>
       </c>
-      <c r="F11" s="9">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+      <c r="H11" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="9"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="6"/>
       <c r="H12" s="6"/>
     </row>
@@ -2917,7 +2917,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
@@ -2930,61 +2930,65 @@
     <col min="8" max="8" width="22.875" customWidth="1"/>
     <col min="9" max="9" width="25.5" customWidth="1"/>
     <col min="10" max="10" width="17.375" customWidth="1"/>
-    <col min="11" max="11" width="16.75" customWidth="1"/>
-    <col min="12" max="12" width="23.375" customWidth="1"/>
-    <col min="13" max="13" width="13.875" customWidth="1"/>
-    <col min="14" max="14" width="54.875" customWidth="1"/>
-    <col min="15" max="15" width="12.25" customWidth="1"/>
+    <col min="11" max="11" width="21.625" customWidth="1"/>
+    <col min="12" max="12" width="16.75" customWidth="1"/>
+    <col min="13" max="13" width="23.375" customWidth="1"/>
+    <col min="14" max="14" width="13.875" customWidth="1"/>
+    <col min="15" max="15" width="54.875" customWidth="1"/>
+    <col min="16" max="16" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:15">
+    <row r="1" ht="14.25" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:15">
+    <row r="2" ht="14.25" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -3028,10 +3032,13 @@
         <v>178</v>
       </c>
       <c r="O2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="P2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:15">
+    <row r="3" ht="14.25" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -3045,25 +3052,25 @@
         <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>22</v>
+        <v>184</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>22</v>
@@ -3072,13 +3079,16 @@
         <v>22</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:15">
+    <row r="4" ht="14.25" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
@@ -3124,8 +3134,11 @@
       <c r="O4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:15">
+      <c r="P4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:16">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
@@ -3150,9 +3163,7 @@
       <c r="J5" s="3">
         <v>0</v>
       </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
+      <c r="K5" s="3"/>
       <c r="L5" s="3">
         <v>0</v>
       </c>
@@ -3165,17 +3176,20 @@
       <c r="O5" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="P5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6" s="4"/>
       <c r="B6" s="4">
         <v>1</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E6" s="4">
         <v>1</v>
@@ -3190,43 +3204,46 @@
         <v>0</v>
       </c>
       <c r="I6" s="4">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4">
         <v>2</v>
       </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
-        <v>1</v>
-      </c>
       <c r="L6" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="4">
-        <v>1</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="O6" s="4">
-        <v>1</v>
-      </c>
-      <c r="P6" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="4">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
-    </row>
-    <row r="7" spans="1:21">
+      <c r="V6" s="4"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7" s="4"/>
       <c r="B7" s="4">
         <v>2</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -3247,40 +3264,43 @@
         <v>0</v>
       </c>
       <c r="K7" s="4">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L7" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="M7" s="4">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="O7" s="4">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="P7" s="4">
+        <v>1</v>
+      </c>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
-    </row>
-    <row r="8" spans="1:21">
+      <c r="V7" s="4"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8" s="4"/>
       <c r="B8" s="4">
         <v>3</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E8" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
         <v>1</v>
@@ -3298,7 +3318,7 @@
         <v>7</v>
       </c>
       <c r="K8" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L8" s="4">
         <v>1</v>
@@ -3306,32 +3326,35 @@
       <c r="M8" s="4">
         <v>1</v>
       </c>
-      <c r="N8" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="O8" s="4">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4"/>
+      <c r="N8" s="4">
+        <v>1</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="P8" s="4">
+        <v>1</v>
+      </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
-    </row>
-    <row r="9" spans="1:21">
+      <c r="V8" s="4"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9" s="4"/>
       <c r="B9" s="4">
         <v>4</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E9" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
         <v>1</v>
@@ -3349,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="4">
         <v>1</v>
@@ -3357,29 +3380,32 @@
       <c r="M9" s="4">
         <v>1</v>
       </c>
-      <c r="N9" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="O9" s="4">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4"/>
+      <c r="N9" s="4">
+        <v>1</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="P9" s="4">
+        <v>1</v>
+      </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
-    </row>
-    <row r="10" spans="1:21">
+      <c r="V9" s="4"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10" s="4"/>
       <c r="B10" s="4">
         <v>5</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -3400,37 +3426,40 @@
         <v>0</v>
       </c>
       <c r="K10" s="4">
+        <v>3</v>
+      </c>
+      <c r="L10" s="4">
         <v>50</v>
       </c>
-      <c r="L10" s="4">
-        <v>0</v>
-      </c>
       <c r="M10" s="4">
-        <v>1</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="O10" s="4">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="P10" s="4">
+        <v>1</v>
+      </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10" s="4"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11" s="4"/>
       <c r="B11" s="4">
         <v>6</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -3451,40 +3480,43 @@
         <v>0</v>
       </c>
       <c r="K11" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" s="4">
-        <v>1</v>
-      </c>
-      <c r="N11" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="O11" s="4">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <v>1</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="P11" s="4">
+        <v>1</v>
+      </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
-    </row>
-    <row r="12" spans="1:21">
+      <c r="V11" s="4"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="4"/>
       <c r="B12" s="4">
         <v>7</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E12" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12" s="4">
         <v>1</v>
@@ -3499,10 +3531,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K12" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L12" s="4">
         <v>1</v>
@@ -3510,20 +3542,23 @@
       <c r="M12" s="4">
         <v>1</v>
       </c>
-      <c r="N12" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="O12" s="4">
-        <v>1</v>
-      </c>
-      <c r="P12" s="4"/>
+      <c r="N12" s="4">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="P12" s="4">
+        <v>1</v>
+      </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
-    </row>
-    <row r="13" spans="1:21">
+      <c r="V12" s="4"/>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -3545,6 +3580,7 @@
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
       <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3585,7 +3621,7 @@
       <c r="E1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -3709,74 +3745,74 @@
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="13" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>2</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
         <v>2</v>
       </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="6">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -3791,7 +3827,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="11.125" customWidth="1"/>
@@ -3880,142 +3916,156 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>2</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="6">
         <v>3</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>4</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="8">
+      <c r="B10" s="6">
         <v>5</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="6">
         <v>5</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="8">
+      <c r="B11" s="6">
         <v>6</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>7</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="8">
+      <c r="B12" s="6">
         <v>7</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>63</v>
       </c>
       <c r="D12" s="6">
         <v>8</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="8">
+      <c r="B13" s="6">
         <v>8</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D13" s="6">
         <v>13</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="8">
+      <c r="B14" s="6">
         <v>9</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="6">
         <v>14</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="8">
+      <c r="B15" s="6">
         <v>10</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="5" t="s">
         <v>66</v>
       </c>
       <c r="D15" s="6">
         <v>15</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" spans="2:5">
+      <c r="B16" s="6">
+        <v>11</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" s="6">
+        <v>6</v>
+      </c>
+      <c r="E16" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4044,13 +4094,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>10</v>
@@ -4061,11 +4111,11 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>20</v>
@@ -4080,7 +4130,7 @@
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>22</v>
@@ -4115,16 +4165,16 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4138,8 +4188,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="16.375" customWidth="1"/>
@@ -4152,17 +4202,17 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>28</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" ht="14.25" spans="1:5">
@@ -4170,14 +4220,14 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" ht="14.25" spans="1:7">
@@ -4194,7 +4244,7 @@
       <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="8"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" ht="14.25" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4215,56 +4265,59 @@
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="7"/>
       <c r="E5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4295,25 +4348,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="14" t="s">
         <v>78</v>
       </c>
+      <c r="F1" s="11" t="s">
+        <v>79</v>
+      </c>
       <c r="G1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>10</v>
@@ -4324,23 +4377,23 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>20</v>
@@ -4358,7 +4411,7 @@
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>22</v>
@@ -4367,7 +4420,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>22</v>
@@ -4426,28 +4479,28 @@
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
         <v>1101</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="D6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>50</v>
       </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
         <v>1</v>
       </c>
     </row>
@@ -4481,31 +4534,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
@@ -4516,7 +4569,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>36</v>
@@ -4525,22 +4578,22 @@
         <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>20</v>
@@ -4569,10 +4622,10 @@
         <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>22</v>
@@ -4644,118 +4697,124 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
         <v>24</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="6">
         <v>6</v>
       </c>
-      <c r="G6" s="8">
-        <v>0</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <v>2</v>
       </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8">
-        <v>1</v>
-      </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>36</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="6">
         <v>8</v>
       </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6">
         <v>4</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="6">
         <v>2</v>
       </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8">
-        <v>1</v>
-      </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
+      <c r="J7" s="6">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
         <v>50</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="6">
         <v>7</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>2</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="6">
         <v>2</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="6">
         <v>3</v>
       </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8">
-        <v>1</v>
-      </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
+      <c r="J8" s="6">
+        <v>0</v>
+      </c>
+      <c r="K8" s="6">
+        <v>1</v>
+      </c>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4767,7 +4826,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="20.875" customWidth="1"/>
@@ -4783,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>108</v>
@@ -4806,10 +4865,10 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>111</v>
@@ -4884,212 +4943,239 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="B6" s="4">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="8">
-        <v>1</v>
-      </c>
-      <c r="C7" s="12">
+      <c r="B7" s="4">
         <v>2</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="C7" s="6">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="8">
-        <v>1</v>
-      </c>
-      <c r="C8" s="12">
+      <c r="B8" s="4">
         <v>3</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="8">
+      <c r="B9" s="4">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6">
         <v>2</v>
       </c>
-      <c r="C9" s="12">
-        <v>4</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="8">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="8">
+      <c r="B10" s="4">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6">
         <v>2</v>
       </c>
-      <c r="C10" s="12">
-        <v>5</v>
-      </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="6">
         <v>3</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="8">
+      <c r="B11" s="4">
+        <v>6</v>
+      </c>
+      <c r="C11" s="6">
         <v>2</v>
       </c>
-      <c r="C11" s="12">
-        <v>6</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="8">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="4">
+        <v>7</v>
+      </c>
+      <c r="C12" s="6">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7">
-      <c r="B12" s="8">
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="4">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6">
         <v>3</v>
       </c>
-      <c r="C12" s="12">
-        <v>7</v>
-      </c>
-      <c r="D12" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G12" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7">
-      <c r="B13" s="6">
-        <v>3</v>
-      </c>
-      <c r="C13" s="12">
-        <v>8</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>125</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="4">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="G13" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7">
-      <c r="B14" s="8">
-        <v>3</v>
-      </c>
-      <c r="C14" s="12">
-        <v>9</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>127</v>
       </c>
       <c r="E14" s="6">
         <v>2</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="4">
+        <v>10</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7">
-      <c r="B15" s="6">
-        <v>3</v>
-      </c>
-      <c r="C15" s="12">
-        <v>10</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="E15" s="6">
         <v>5</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="G15" s="8">
+      <c r="F15" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" s="6"/>
-      <c r="C16" s="12"/>
+      <c r="C16" s="4"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="4"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="4"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="4"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="4"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="4"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="4"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="4"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="4"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5121,28 +5207,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>10</v>
@@ -5153,26 +5239,26 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>20</v>
@@ -5187,7 +5273,7 @@
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>22</v>
@@ -5265,104 +5351,104 @@
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="8">
-        <v>1</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6">
         <v>100</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="6">
         <v>80</v>
       </c>
-      <c r="H6" s="8">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8">
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="6">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
         <v>1</v>
       </c>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <v>2</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="C7" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6">
         <v>100</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="6">
         <v>80</v>
       </c>
-      <c r="H7" s="8">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8">
-        <v>1</v>
-      </c>
-      <c r="J7" s="8">
+      <c r="H7" s="6">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6">
         <v>1</v>
       </c>
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <v>3</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="C8" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6">
         <v>100</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="6">
         <v>80</v>
       </c>
-      <c r="H8" s="8">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8">
-        <v>1</v>
-      </c>
-      <c r="J8" s="8">
+      <c r="H8" s="6">
+        <v>1</v>
+      </c>
+      <c r="I8" s="6">
+        <v>1</v>
+      </c>
+      <c r="J8" s="6">
         <v>1</v>
       </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="8">
+      <c r="B9" s="6">
         <v>4</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>147</v>
+      <c r="C9" s="9" t="s">
+        <v>146</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -5370,41 +5456,41 @@
       <c r="E9" s="6">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="6">
         <v>100</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="6">
         <v>80</v>
       </c>
-      <c r="H9" s="8">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="8">
+      <c r="H9" s="6">
+        <v>1</v>
+      </c>
+      <c r="I9" s="6">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6">
         <v>1</v>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="10:10">
-      <c r="J10" s="8"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" spans="10:10">
-      <c r="J11" s="8"/>
+      <c r="J11" s="6"/>
     </row>
     <row r="12" spans="10:10">
-      <c r="J12" s="8"/>
+      <c r="J12" s="6"/>
     </row>
     <row r="13" spans="10:10">
-      <c r="J13" s="8"/>
+      <c r="J13" s="6"/>
     </row>
     <row r="14" spans="10:10">
-      <c r="J14" s="8"/>
+      <c r="J14" s="6"/>
     </row>
     <row r="15" spans="10:10">
-      <c r="J15" s="8"/>
+      <c r="J15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Datas/B-战斗配置表.xlsx
+++ b/Datas/B-战斗配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="battle_rule" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="combat_scenario" sheetId="9" r:id="rId9"/>
     <sheet name="combat_scenario_enemy" sheetId="10" r:id="rId10"/>
     <sheet name="status" sheetId="11" r:id="rId11"/>
+    <sheet name="element_stone" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +79,7 @@
     <author>杨宗水</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0">
+    <comment ref="D2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -91,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0">
+    <comment ref="I2" authorId="0">
       <text>
         <r>
           <rPr>
@@ -252,6 +253,42 @@
 3:百分比
 4:标记型
 </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments12.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>杨宗水</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>中文名
+方便策划维护</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0：不用
+1：启用</t>
         </r>
       </text>
     </comment>
@@ -702,7 +739,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="233">
   <si>
     <t>##comment</t>
   </si>
@@ -1145,6 +1182,9 @@
     <t>Debug三怪混战</t>
   </si>
   <si>
+    <t>ID</t>
+  </si>
+  <si>
     <t>顺序</t>
   </si>
   <si>
@@ -1154,6 +1194,9 @@
     <t>初始血量倍率</t>
   </si>
   <si>
+    <t>id</t>
+  </si>
+  <si>
     <t>order</t>
   </si>
   <si>
@@ -1320,6 +1363,81 @@
   </si>
   <si>
     <t>行动前触发；MVP可表现为跳过或削弱下一次行动</t>
+  </si>
+  <si>
+    <t>属性石ID</t>
+  </si>
+  <si>
+    <t>纯度档</t>
+  </si>
+  <si>
+    <t>纯度下限</t>
+  </si>
+  <si>
+    <t>纯度上限</t>
+  </si>
+  <si>
+    <t>注灵伤害倍率</t>
+  </si>
+  <si>
+    <t>注灵消耗耐久</t>
+  </si>
+  <si>
+    <t>轻微效果组</t>
+  </si>
+  <si>
+    <t>stone_id</t>
+  </si>
+  <si>
+    <t>purity_grade</t>
+  </si>
+  <si>
+    <t>purity_min</t>
+  </si>
+  <si>
+    <t>purity_max</t>
+  </si>
+  <si>
+    <t>damage_rate</t>
+  </si>
+  <si>
+    <t>durability_cost</t>
+  </si>
+  <si>
+    <t>minor_effect_group</t>
+  </si>
+  <si>
+    <t>EPurityGrade</t>
+  </si>
+  <si>
+    <t>金属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>3,1,3,6</t>
+  </si>
+  <si>
+    <t>木属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>3,2,3,3</t>
+  </si>
+  <si>
+    <t>水属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>3,1,3,2</t>
+  </si>
+  <si>
+    <t>火属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>3,2,3,4</t>
+  </si>
+  <si>
+    <t>土属性石·一阶·普通</t>
+  </si>
+  <si>
+    <t>2,4,1</t>
   </si>
 </sst>
 </file>
@@ -1970,29 +2088,29 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2333,10 +2451,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -2365,7 +2483,7 @@
       <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
@@ -2398,7 +2516,7 @@
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
@@ -2431,7 +2549,7 @@
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2462,7 +2580,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="7"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3">
         <v>0</v>
       </c>
@@ -2489,7 +2607,7 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="6">
+      <c r="B6" s="7">
         <v>1</v>
       </c>
       <c r="C6" t="s">
@@ -2531,79 +2649,85 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="18.5" customWidth="1"/>
-    <col min="3" max="3" width="19.875" customWidth="1"/>
-    <col min="4" max="4" width="22.25" customWidth="1"/>
-    <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="1" max="2" width="13.75" customWidth="1"/>
+    <col min="3" max="3" width="18.5" customWidth="1"/>
+    <col min="4" max="4" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="15.25" customWidth="1"/>
+    <col min="7" max="7" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:8">
+    <row r="1" ht="14.25" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="14.25" spans="1:8">
+    <row r="2" ht="14.25" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="3" t="s">
-        <v>150</v>
-      </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:8">
+    <row r="3" ht="14.25" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
@@ -2611,23 +2735,26 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" spans="1:8">
+        <v>155</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7"/>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2640,272 +2767,294 @@
       <c r="H4" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" spans="1:8">
+      <c r="I4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3">
         <v>0</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
         <v>1</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" s="6">
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
       <c r="G7" s="6">
         <v>1</v>
       </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" s="6">
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="4">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
+        <v>1</v>
+      </c>
+      <c r="F8" s="5">
         <v>3</v>
       </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
       <c r="G8" s="6">
         <v>1</v>
       </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" s="6">
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="7">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="4">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="E9" s="5">
+        <v>1</v>
+      </c>
+      <c r="F9" s="5">
         <v>1</v>
       </c>
       <c r="G9" s="6">
         <v>1</v>
       </c>
-      <c r="H9" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" s="6">
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="7">
         <v>5</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="7">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="4">
+      <c r="E10" s="5">
         <v>2</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="5">
         <v>2</v>
       </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
       <c r="G10" s="6">
         <v>1</v>
       </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" s="6">
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="7">
         <v>6</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="7">
+        <v>4</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="D11" s="4">
+      <c r="E11" s="5">
         <v>3</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="5">
         <v>3</v>
       </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
       <c r="G11" s="6">
         <v>1</v>
       </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9">
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="2:8">
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="2:8">
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+    </row>
+    <row r="13" spans="3:9">
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+    </row>
+    <row r="14" spans="3:9">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" spans="3:9">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" spans="3:9">
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="3:9">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="3:9">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="3:9">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+    </row>
+    <row r="20" spans="3:9">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+    </row>
+    <row r="21" spans="3:9">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="3:9">
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="3:9">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2943,48 +3092,48 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>159</v>
       </c>
+      <c r="F1" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>161</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J1" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="J1" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="K1" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="L1" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="M1" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="N1" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="P1" s="8" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2993,7 +3142,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>36</v>
@@ -3002,37 +3151,37 @@
         <v>37</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>20</v>
@@ -3052,25 +3201,25 @@
         <v>42</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>22</v>
@@ -3181,406 +3330,815 @@
       </c>
     </row>
     <row r="6" spans="1:22">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E6" s="5">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5">
+        <v>1</v>
+      </c>
+      <c r="G6" s="5">
         <v>999</v>
       </c>
-      <c r="H6" s="4">
-        <v>0</v>
-      </c>
-      <c r="I6" s="4">
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
         <v>3</v>
       </c>
-      <c r="J6" s="4">
-        <v>0</v>
-      </c>
-      <c r="K6" s="4">
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
         <v>2</v>
       </c>
-      <c r="L6" s="4">
-        <v>1</v>
-      </c>
-      <c r="M6" s="4">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <v>1</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="P6" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
-      <c r="V6" s="4"/>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
     </row>
     <row r="7" spans="1:22">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="C7" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E7" s="5">
         <v>2</v>
       </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
         <v>999</v>
       </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
         <v>3</v>
       </c>
-      <c r="J7" s="4">
-        <v>0</v>
-      </c>
-      <c r="K7" s="4">
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
         <v>3</v>
       </c>
-      <c r="L7" s="4">
-        <v>25</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="P7" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
+      <c r="L7" s="5">
+        <v>25</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="C8" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="5">
         <v>3</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5">
         <v>999</v>
       </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="4">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4">
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
         <v>7</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="5">
         <v>2</v>
       </c>
-      <c r="L8" s="4">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4">
-        <v>1</v>
-      </c>
-      <c r="N8" s="4">
-        <v>1</v>
-      </c>
-      <c r="O8" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="P8" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
-      <c r="V8" s="4"/>
+      <c r="L8" s="5">
+        <v>1</v>
+      </c>
+      <c r="M8" s="5">
+        <v>1</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
     </row>
     <row r="9" spans="1:22">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="C9" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="5">
         <v>3</v>
       </c>
-      <c r="F9" s="4">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="F9" s="5">
+        <v>1</v>
+      </c>
+      <c r="G9" s="5">
         <v>999</v>
       </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4">
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
         <v>2</v>
       </c>
-      <c r="L9" s="4">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4">
-        <v>1</v>
-      </c>
-      <c r="N9" s="4">
-        <v>1</v>
-      </c>
-      <c r="O9" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="P9" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
+      <c r="L9" s="5">
+        <v>1</v>
+      </c>
+      <c r="M9" s="5">
+        <v>1</v>
+      </c>
+      <c r="N9" s="5">
+        <v>1</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="P9" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
     </row>
     <row r="10" spans="1:22">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5">
         <v>5</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="C10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="5">
         <v>2</v>
       </c>
-      <c r="F10" s="4">
-        <v>1</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
         <v>999</v>
       </c>
-      <c r="H10" s="4">
-        <v>0</v>
-      </c>
-      <c r="I10" s="4">
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
         <v>4</v>
       </c>
-      <c r="J10" s="4">
-        <v>0</v>
-      </c>
-      <c r="K10" s="4">
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
         <v>3</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="5">
         <v>50</v>
       </c>
-      <c r="M10" s="4">
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <v>1</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="P10" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="P10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
     </row>
     <row r="11" spans="1:22">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5">
         <v>6</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="C11" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" s="5">
         <v>2</v>
       </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4">
+      <c r="F11" s="5">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5">
         <v>999</v>
       </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
         <v>4</v>
       </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
         <v>2</v>
       </c>
-      <c r="L11" s="4">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <v>1</v>
-      </c>
-      <c r="O11" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="P11" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
+      <c r="L11" s="5">
+        <v>1</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>1</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P11" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
     </row>
     <row r="12" spans="1:22">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="C12" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="E12" s="5">
         <v>4</v>
       </c>
-      <c r="F12" s="4">
-        <v>1</v>
-      </c>
-      <c r="G12" s="4">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5">
         <v>3</v>
       </c>
-      <c r="I12" s="4">
-        <v>1</v>
-      </c>
-      <c r="J12" s="4">
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
         <v>10</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="5">
         <v>4</v>
       </c>
-      <c r="L12" s="4">
-        <v>1</v>
-      </c>
-      <c r="M12" s="4">
-        <v>1</v>
-      </c>
-      <c r="N12" s="4">
-        <v>1</v>
-      </c>
-      <c r="O12" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="P12" s="4">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
-      <c r="V12" s="4"/>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+      <c r="O12" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="P12" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
     </row>
     <row r="13" spans="1:22">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="15.375" customWidth="1"/>
+    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="6" width="10.75" customWidth="1"/>
+    <col min="7" max="8" width="16.125" customWidth="1"/>
+    <col min="9" max="9" width="16.625" customWidth="1"/>
+    <col min="10" max="10" width="15.375" customWidth="1"/>
+    <col min="11" max="11" width="18.125" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="14.25" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" ht="14.25" spans="1:13">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" spans="1:13">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" spans="1:13">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" ht="14.25" spans="1:13">
+      <c r="A5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="5">
+        <v>4112</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2112</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>2</v>
+      </c>
+      <c r="H6" s="7">
+        <v>50</v>
+      </c>
+      <c r="I6" s="7">
+        <v>69</v>
+      </c>
+      <c r="J6" s="7">
+        <v>100</v>
+      </c>
+      <c r="K6" s="7">
+        <v>5</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="5">
+        <v>4122</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2122</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>2</v>
+      </c>
+      <c r="H7" s="7">
+        <v>50</v>
+      </c>
+      <c r="I7" s="7">
+        <v>69</v>
+      </c>
+      <c r="J7" s="7">
+        <v>100</v>
+      </c>
+      <c r="K7" s="7">
+        <v>5</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="5">
+        <v>4132</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2132</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="7">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1</v>
+      </c>
+      <c r="G8" s="7">
+        <v>2</v>
+      </c>
+      <c r="H8" s="7">
+        <v>50</v>
+      </c>
+      <c r="I8" s="7">
+        <v>69</v>
+      </c>
+      <c r="J8" s="7">
+        <v>100</v>
+      </c>
+      <c r="K8" s="7">
+        <v>5</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="5">
+        <v>4142</v>
+      </c>
+      <c r="C9" s="5">
+        <v>2142</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2</v>
+      </c>
+      <c r="H9" s="7">
+        <v>50</v>
+      </c>
+      <c r="I9" s="7">
+        <v>69</v>
+      </c>
+      <c r="J9" s="7">
+        <v>100</v>
+      </c>
+      <c r="K9" s="7">
+        <v>5</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="5">
+        <v>4152</v>
+      </c>
+      <c r="C10" s="5">
+        <v>2152</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="7">
+        <v>5</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7">
+        <v>2</v>
+      </c>
+      <c r="H10" s="7">
+        <v>50</v>
+      </c>
+      <c r="I10" s="7">
+        <v>69</v>
+      </c>
+      <c r="J10" s="7">
+        <v>100</v>
+      </c>
+      <c r="K10" s="7">
+        <v>5</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="M10" s="7">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3618,10 +4176,10 @@
       <c r="D1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -3745,74 +4303,74 @@
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:9">
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7">
         <v>2</v>
       </c>
-      <c r="F7" s="6">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="F7" s="7">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+      <c r="H7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:9">
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
         <v>2</v>
       </c>
-      <c r="G8" s="6">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="s">
+      <c r="G8" s="7">
+        <v>1</v>
+      </c>
+      <c r="H8" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>1</v>
       </c>
     </row>
@@ -3916,156 +4474,156 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="7">
         <v>2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>3</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>4</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <v>5</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>5</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="6">
+      <c r="B11" s="7">
         <v>6</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>7</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>7</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>8</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <v>8</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>13</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <v>9</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>14</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="6">
+      <c r="B15" s="7">
         <v>10</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="7">
         <v>15</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="2:5">
-      <c r="B16" s="6">
+      <c r="B16" s="7">
         <v>11</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="7">
         <v>6</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4099,7 +4657,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -4113,7 +4671,7 @@
       <c r="B2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>71</v>
       </c>
@@ -4128,7 +4686,7 @@
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
         <v>72</v>
       </c>
@@ -4143,7 +4701,7 @@
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
@@ -4156,7 +4714,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="7"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3">
         <v>0</v>
       </c>
@@ -4165,16 +4723,16 @@
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4202,7 +4760,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -4211,7 +4769,7 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>74</v>
       </c>
     </row>
@@ -4225,7 +4783,7 @@
       <c r="C2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="3" t="s">
         <v>75</v>
       </c>
@@ -4240,11 +4798,11 @@
       <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="7"/>
     </row>
     <row r="4" ht="14.25" spans="1:5">
       <c r="A4" s="1" t="s">
@@ -4256,7 +4814,7 @@
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
@@ -4269,55 +4827,55 @@
         <v>0</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:2">
-      <c r="B26" s="6"/>
+      <c r="B26" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4356,10 +4914,10 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -4382,7 +4940,7 @@
       <c r="C2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="3" t="s">
         <v>84</v>
       </c>
@@ -4409,7 +4967,7 @@
       <c r="C3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="3" t="s">
         <v>88</v>
       </c>
@@ -4436,7 +4994,7 @@
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="7"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="3" t="s">
         <v>25</v>
       </c>
@@ -4461,7 +5019,7 @@
       <c r="C5" s="3">
         <v>0</v>
       </c>
-      <c r="D5" s="7"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="3">
         <v>0</v>
       </c>
@@ -4479,28 +5037,28 @@
       </c>
     </row>
     <row r="6" spans="2:9">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
         <v>1101</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
         <v>50</v>
       </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6">
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
         <v>1</v>
       </c>
     </row>
@@ -4536,10 +5094,10 @@
       <c r="B1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
@@ -4697,124 +5255,124 @@
       </c>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7">
         <v>24</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <v>6</v>
       </c>
-      <c r="G6" s="6">
-        <v>0</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="G6" s="7">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7">
         <v>2</v>
       </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7">
         <v>36</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <v>8</v>
       </c>
-      <c r="G7" s="6">
-        <v>1</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="G7" s="7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="7">
         <v>4</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="7">
         <v>2</v>
       </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>1</v>
-      </c>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1</v>
+      </c>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7">
         <v>50</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <v>7</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>2</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="7">
         <v>2</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="7">
         <v>3</v>
       </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>1</v>
-      </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>1</v>
+      </c>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4943,239 +5501,239 @@
       </c>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="4">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="10" t="s">
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:7">
-      <c r="B7" s="4">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:7">
-      <c r="B8" s="4">
+      <c r="B8" s="5">
         <v>3</v>
       </c>
-      <c r="C8" s="6">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="s">
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:7">
-      <c r="B9" s="4">
+      <c r="B9" s="5">
         <v>4</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <v>2</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:7">
-      <c r="B10" s="4">
+      <c r="B10" s="5">
         <v>5</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <v>2</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="7">
         <v>3</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:7">
-      <c r="B11" s="4">
+      <c r="B11" s="5">
         <v>6</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>2</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:7">
-      <c r="B12" s="4">
+      <c r="B12" s="5">
         <v>7</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="7">
         <v>3</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="6">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="E12" s="7">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:7">
-      <c r="B13" s="4">
+      <c r="B13" s="5">
         <v>8</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <v>3</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="7">
         <v>4</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:7">
-      <c r="B14" s="4">
+      <c r="B14" s="5">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="7">
         <v>2</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:7">
-      <c r="B15" s="4">
+      <c r="B15" s="5">
         <v>10</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="7">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="7">
         <v>5</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:7">
-      <c r="B16" s="6"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="34" spans="2:2">
-      <c r="B34" s="4"/>
+      <c r="B34" s="5"/>
     </row>
     <row r="35" spans="2:2">
-      <c r="B35" s="4"/>
+      <c r="B35" s="5"/>
     </row>
     <row r="36" spans="2:2">
-      <c r="B36" s="4"/>
+      <c r="B36" s="5"/>
     </row>
     <row r="37" spans="2:2">
-      <c r="B37" s="4"/>
+      <c r="B37" s="5"/>
     </row>
     <row r="38" spans="2:2">
-      <c r="B38" s="4"/>
+      <c r="B38" s="5"/>
     </row>
     <row r="39" spans="2:2">
-      <c r="B39" s="4"/>
+      <c r="B39" s="5"/>
     </row>
     <row r="40" spans="2:2">
-      <c r="B40" s="4"/>
+      <c r="B40" s="5"/>
     </row>
     <row r="41" spans="2:2">
-      <c r="B41" s="4"/>
+      <c r="B41" s="5"/>
     </row>
     <row r="42" spans="2:2">
-      <c r="B42" s="4"/>
+      <c r="B42" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5212,22 +5770,22 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="8" t="s">
         <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -5241,7 +5799,7 @@
       <c r="B2" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
         <v>138</v>
       </c>
@@ -5271,7 +5829,7 @@
       <c r="B3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
         <v>142</v>
       </c>
@@ -5301,7 +5859,7 @@
       <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
@@ -5329,7 +5887,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="7"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3">
         <v>0</v>
       </c>
@@ -5351,146 +5909,146 @@
       </c>
     </row>
     <row r="6" spans="2:12">
-      <c r="B6" s="6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
         <v>100</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="7">
         <v>80</v>
       </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="6">
+      <c r="B7" s="7">
         <v>2</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
         <v>100</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="7">
         <v>80</v>
       </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" s="6">
-        <v>1</v>
-      </c>
-      <c r="J7" s="6">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6"/>
-      <c r="L7" s="6"/>
+      <c r="H7" s="7">
+        <v>1</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="6">
+      <c r="B8" s="7">
         <v>3</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="6">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="6">
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="7">
         <v>100</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="7">
         <v>80</v>
       </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6">
-        <v>1</v>
-      </c>
-      <c r="J8" s="6">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
+      <c r="H8" s="7">
+        <v>1</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <v>4</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="7">
         <v>100</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="7">
         <v>80</v>
       </c>
-      <c r="H9" s="6">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
     </row>
     <row r="10" spans="10:10">
-      <c r="J10" s="6"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="10:10">
-      <c r="J11" s="6"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="10:10">
-      <c r="J12" s="6"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="10:10">
-      <c r="J13" s="6"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="10:10">
-      <c r="J14" s="6"/>
+      <c r="J14" s="7"/>
     </row>
     <row r="15" spans="10:10">
-      <c r="J15" s="6"/>
+      <c r="J15" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
